--- a/data/Terre di Pedemonte/investment_decision/Tegna_MFH_2005-2014_investment_decision.xlsx
+++ b/data/Terre di Pedemonte/investment_decision/Tegna_MFH_2005-2014_investment_decision.xlsx
@@ -461,22 +461,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>28.73456768192426</v>
+        <v>6.80883468406618</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,19 +509,19 @@
         <v>4447.099540827093</v>
       </c>
       <c r="F2" t="n">
-        <v>31.93304986281105</v>
+        <v>6.966808853757339</v>
       </c>
       <c r="G2" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="H2" t="n">
-        <v>28.73456768192426</v>
+        <v>7.040926551989862</v>
       </c>
       <c r="I2" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="J2" t="n">
-        <v>31.93304986281105</v>
+        <v>7.166365275276725</v>
       </c>
       <c r="K2" t="n">
         <v>4447.099540827093</v>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>28.73456768192426</v>
+        <v>6.80883468406618</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>4447.099540827093</v>
       </c>
       <c r="F3" t="n">
-        <v>32.05323899669663</v>
+        <v>6.966808853757339</v>
       </c>
       <c r="G3" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="H3" t="n">
-        <v>28.73456768192426</v>
+        <v>7.040926551989862</v>
       </c>
       <c r="I3" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="J3" t="n">
-        <v>32.05323899669661</v>
+        <v>7.166365275276725</v>
       </c>
       <c r="K3" t="n">
         <v>4447.099540827093</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>28.73456768192426</v>
+        <v>12.16551712991648</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>4447.099540827093</v>
       </c>
       <c r="F4" t="n">
-        <v>33.8893327892468</v>
+        <v>13.06287685687147</v>
       </c>
       <c r="G4" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="H4" t="n">
-        <v>28.73456768192426</v>
+        <v>10.40420668042175</v>
       </c>
       <c r="I4" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="J4" t="n">
-        <v>33.9529386380627</v>
+        <v>12.52992117379445</v>
       </c>
       <c r="K4" t="n">
         <v>4447.099540827093</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>28.83432075406855</v>
+        <v>16.11355419704524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>4447.099540827093</v>
       </c>
       <c r="F5" t="n">
-        <v>33.8893327892468</v>
+        <v>15.97977406041887</v>
       </c>
       <c r="G5" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="H5" t="n">
-        <v>28.83432075406856</v>
+        <v>15.48404969421577</v>
       </c>
       <c r="I5" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="J5" t="n">
-        <v>33.9529386380627</v>
+        <v>15.50121651674369</v>
       </c>
       <c r="K5" t="n">
         <v>4447.099540827093</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>28.83432075406855</v>
+        <v>16.11355419704524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>4447.099540827093</v>
       </c>
       <c r="F6" t="n">
-        <v>33.8893327892468</v>
+        <v>15.97977406041887</v>
       </c>
       <c r="G6" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="H6" t="n">
-        <v>28.83432075406856</v>
+        <v>15.48404969421577</v>
       </c>
       <c r="I6" t="n">
         <v>4447.099540827093</v>
       </c>
       <c r="J6" t="n">
-        <v>33.9529386380627</v>
+        <v>15.50121651674369</v>
       </c>
       <c r="K6" t="n">
         <v>4447.099540827093</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>6.670649311240639</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.798664548438639</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>6.670649311240639</v>
+        <v>9.598152509518826</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.798664548438639</v>
+        <v>9.598152509518826</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>6.670649311240639</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.624054151055932</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>6.670649311240639</v>
+        <v>11.68367893194225</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.624054151055932</v>
+        <v>11.68367893194225</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>6.670649311240639</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.962158623884313</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>6.670649311240639</v>
+        <v>12.53797344860104</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.962158623884313</v>
+        <v>12.53797344860104</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>6.670649311240639</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5.14289093730125</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6.670649311240639</v>
+        <v>12.99463296287347</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5.14289093730125</v>
+        <v>12.99463296287347</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Tegna_b_MFH_2005-2014</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Tegna_b_MFH_2005-2014</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>6.670649311240639</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.255825328669338</v>
+        <v>16.85484691011236</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>6.670649311240639</v>
+        <v>13.2799862753596</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5.255825328669338</v>
+        <v>13.2799862753596</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.002936629891764706</v>
+        <v>0.00208011284</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1050,7 +1050,7 @@
         <v>46023</v>
       </c>
       <c r="B17" t="n">
-        <v>0.05783422524547985</v>
+        <v>0.07800423149999999</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03899100510852809</v>
+        <v>0.07750663347964136</v>
       </c>
       <c r="G17" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05783422524547984</v>
+        <v>0.07550232300655647</v>
       </c>
       <c r="I17" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03899100510852809</v>
+        <v>0.07475774259379833</v>
       </c>
       <c r="K17" t="n">
         <v>0.4368236964</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.22101198925</v>
+        <v>0.1243812166378004</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2340126945</v>
+        <v>0.1223138169492516</v>
       </c>
       <c r="G18" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H18" t="n">
-        <v>0.22101198925</v>
+        <v>0.1079325097524231</v>
       </c>
       <c r="I18" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2340126945</v>
+        <v>0.1069890591792051</v>
       </c>
       <c r="K18" t="n">
         <v>0.4368236964</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3380183365</v>
+        <v>0.19501057875</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3380183365</v>
+        <v>0.1960039694627133</v>
       </c>
       <c r="G19" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3380183365</v>
+        <v>0.1709214118646104</v>
       </c>
       <c r="I19" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3380183365</v>
+        <v>0.1803917646582361</v>
       </c>
       <c r="K19" t="n">
         <v>0.4368236964</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2801841112545201</v>
+        <v>0.1283716144077501</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2990273313914719</v>
+        <v>0.1283716144077501</v>
       </c>
       <c r="G20" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2801841112545201</v>
+        <v>0.1043858257295572</v>
       </c>
       <c r="I20" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2990273313914719</v>
+        <v>0.1056340220644378</v>
       </c>
       <c r="K20" t="n">
         <v>0.4368236964</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.11700634725</v>
+        <v>0.08199462926994966</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F21" t="n">
-        <v>0.104005642</v>
+        <v>0.08356443093813988</v>
       </c>
       <c r="G21" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1170063472500001</v>
+        <v>0.07195563898369062</v>
       </c>
       <c r="I21" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J21" t="n">
-        <v>0.104005642</v>
+        <v>0.07340270547903097</v>
       </c>
       <c r="K21" t="n">
         <v>0.4368236964</v>
@@ -1420,7 +1420,7 @@
         <v>46023</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1434,19 +1434,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="G27" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="I27" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="K27" t="n">
         <v>0.4368236964</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="G28" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.140992135928193</v>
       </c>
       <c r="I28" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.1397439395933124</v>
       </c>
       <c r="K28" t="n">
         <v>0.4368236964</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.14300775775</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.1420143670372867</v>
       </c>
       <c r="G29" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1670969246353896</v>
       </c>
       <c r="I29" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1576265718417639</v>
       </c>
       <c r="K29" t="n">
         <v>0.4368236964</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="G30" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.1539928411781929</v>
       </c>
       <c r="I30" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.1527446448433124</v>
       </c>
       <c r="K30" t="n">
         <v>0.4368236964</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.4368236964</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.1300070525</v>
       </c>
       <c r="G31" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.14300775775</v>
       </c>
       <c r="I31" t="n">
         <v>0.4368236964</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.14300775775</v>
       </c>
       <c r="K31" t="n">
         <v>0.4368236964</v>
@@ -1992,13 +1992,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
+        <v>3.679882951874126</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>2.133688014010495</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>3.679882951874126</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>3.679882951874126</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>2.594219247858607</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3.679882951874126</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2066,13 +2066,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
+        <v>3.679882951874126</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>2.783878901976278</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>3.679882951874126</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>3.679882951874126</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>2.886689915779936</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>3.679882951874126</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>3.679882951874126</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>2.952026570611213</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>3.679882951874126</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2857306633269243</v>
+        <v>0.2940999167119986</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,19 +2359,19 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F52" t="n">
-        <v>0.324839777560243</v>
+        <v>0.2759343120390992</v>
       </c>
       <c r="G52" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.2811277158331009</v>
+      </c>
+      <c r="I52" t="n">
         <v>0.4169344082527729</v>
       </c>
-      <c r="H52" t="n">
-        <v>0.2648900669279683</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1.328853693416453</v>
-      </c>
       <c r="J52" t="n">
-        <v>0.3122267264941088</v>
+        <v>0.2634636888699108</v>
       </c>
       <c r="K52" t="n">
         <v>0.4169344082527729</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2857306633269243</v>
+        <v>0.2940999167119986</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F53" t="n">
-        <v>0.324839777560243</v>
+        <v>0.2759343120390992</v>
       </c>
       <c r="G53" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2811277158331009</v>
+      </c>
+      <c r="I53" t="n">
         <v>0.548470187161861</v>
       </c>
-      <c r="H53" t="n">
-        <v>0.2648900669279683</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1.328853693416453</v>
-      </c>
       <c r="J53" t="n">
-        <v>0.3122267264941088</v>
+        <v>0.2634636888699108</v>
       </c>
       <c r="K53" t="n">
         <v>0.548470187161861</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.2857306633269243</v>
+        <v>0.2940999167119986</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3248397775602431</v>
+        <v>0.2759343120390992</v>
       </c>
       <c r="G54" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.2811277158331009</v>
+      </c>
+      <c r="I54" t="n">
         <v>0.6070890037359258</v>
       </c>
-      <c r="H54" t="n">
-        <v>0.2648900669279683</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1.328853693416453</v>
-      </c>
       <c r="J54" t="n">
-        <v>0.3122267264941088</v>
+        <v>0.2634636888699108</v>
       </c>
       <c r="K54" t="n">
         <v>0.6070890037359258</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.3359028057967757</v>
+        <v>0.3476429584494563</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3369769683991587</v>
+        <v>0.3356665115907875</v>
       </c>
       <c r="G55" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.3460552602708309</v>
+      </c>
+      <c r="I55" t="n">
         <v>0.6387243061611209</v>
       </c>
-      <c r="H55" t="n">
-        <v>0.3248814172599414</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.328853693416453</v>
-      </c>
       <c r="J55" t="n">
-        <v>0.3248814172599414</v>
+        <v>0.3303214177682295</v>
       </c>
       <c r="K55" t="n">
         <v>0.6387243061611209</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.3359028057967757</v>
+        <v>0.3476429584494563</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3369769683991587</v>
+        <v>0.3356665115907875</v>
       </c>
       <c r="G56" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.3460552602708309</v>
+      </c>
+      <c r="I56" t="n">
         <v>0.6582529809249137</v>
       </c>
-      <c r="H56" t="n">
-        <v>0.3248814172599414</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1.328853693416453</v>
-      </c>
       <c r="J56" t="n">
-        <v>0.3248814172599414</v>
+        <v>0.3303214177682294</v>
       </c>
       <c r="K56" t="n">
         <v>0.6582529809249137</v>
@@ -2547,13 +2547,13 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>0.4169344082527729</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1.328853693416453</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -2584,13 +2584,13 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>0.548470187161861</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1.328853693416453</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2621,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.6070890037359258</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1.328853693416453</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.6387243061611209</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1.328853693416453</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2695,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
+        <v>1.328853693416453</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>0.6582529809249137</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1.328853693416453</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2440824330278682</v>
+        <v>0.1130204514513514</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2206551520599055</v>
+        <v>0.1226756960278762</v>
       </c>
       <c r="G64" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2543407052532143</v>
+        <v>0.1293466641742016</v>
       </c>
       <c r="I64" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="J64" t="n">
-        <v>0.2329700507097152</v>
+        <v>0.122213323688887</v>
       </c>
       <c r="K64" t="n">
         <v>1.328853693416453</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2856984206292781</v>
+        <v>0.1378080932236098</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F65" t="n">
-        <v>0.260928889111997</v>
+        <v>0.150577833375609</v>
       </c>
       <c r="G65" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2967198091661124</v>
+        <v>0.1472935413433983</v>
       </c>
       <c r="I65" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="J65" t="n">
-        <v>0.2727262878348898</v>
+        <v>0.1627088505234876</v>
       </c>
       <c r="K65" t="n">
         <v>1.328853693416453</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.2856984206292781</v>
+        <v>0.1378080932236098</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F66" t="n">
-        <v>0.260928889111997</v>
+        <v>0.150577833375609</v>
       </c>
       <c r="G66" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2967198091661124</v>
+        <v>0.1472935413433983</v>
       </c>
       <c r="I66" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2727262878348898</v>
+        <v>0.1627088505234876</v>
       </c>
       <c r="K66" t="n">
         <v>1.328853693416453</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.04112673516665174</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.04112673516665174</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="73">
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.06369512061536256</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.06369512061536256</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="74">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.07857368956999328</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.07857368956999328</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="75">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.08940797171853594</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.08940797171853594</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="76">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.09779454394511296</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.09779454394511296</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="77">
@@ -3270,7 +3270,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.09225572259693765</v>
+        <v>0.1138543789360224</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,22 +3284,22 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F77" t="n">
-        <v>0.05241092789100715</v>
+        <v>0.1146767705734567</v>
       </c>
       <c r="G77" t="n">
-        <v>0.04112673516665174</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1028380467705475</v>
+        <v>0.1286784513370187</v>
       </c>
       <c r="I77" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="J77" t="n">
-        <v>0.05241092789100715</v>
+        <v>0.1283130338222155</v>
       </c>
       <c r="K77" t="n">
-        <v>0.04112673516665174</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="78">
@@ -3307,7 +3307,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.09225572259693765</v>
+        <v>0.1138543789360224</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,22 +3321,22 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F78" t="n">
-        <v>0.05241092789100715</v>
+        <v>0.1146767705734567</v>
       </c>
       <c r="G78" t="n">
-        <v>0.06369512061536256</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1028380467705475</v>
+        <v>0.1286784513370187</v>
       </c>
       <c r="I78" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="J78" t="n">
-        <v>0.05241092789100715</v>
+        <v>0.1283130338222155</v>
       </c>
       <c r="K78" t="n">
-        <v>0.06369512061536256</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="79">
@@ -3344,7 +3344,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.09225572259693765</v>
+        <v>0.1138543789360224</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,22 +3358,22 @@
         <v>1.328853693416453</v>
       </c>
       <c r="F79" t="n">
-        <v>0.05241092789100715</v>
+        <v>0.1146767705734567</v>
       </c>
       <c r="G79" t="n">
-        <v>0.07857368956999328</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1028380467705475</v>
+        <v>0.1286784513370187</v>
       </c>
       <c r="I79" t="n">
         <v>1.328853693416453</v>
       </c>
       <c r="J79" t="n">
-        <v>0.05241092789100715</v>
+        <v>0.1283130338222155</v>
       </c>
       <c r="K79" t="n">
-        <v>0.07857368956999328</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="80">
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.08940797171853594</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.08940797171853594</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="81">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.09779454394511296</v>
+        <v>1.328853693416453</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.09779454394511296</v>
+        <v>1.328853693416453</v>
       </c>
     </row>
     <row r="82">
@@ -3470,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3505,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -3610,13 +3610,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3645,13 +3645,13 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -3680,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3715,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -3820,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>0.4293250562242569</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3855,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>0.5615523961267772</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>0.624556919057325</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3925,13 +3925,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.6622379613453093</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
         <v>0.6881588528152967</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
